--- a/Assessment Questions/CDE/DATA ENGINEERING ASSOCIATE/DATA ORCHESTRATION WITH APACHE AIRFLOW/TAG and DAG/dag_and_tags_questions.xlsx
+++ b/Assessment Questions/CDE/DATA ENGINEERING ASSOCIATE/DATA ORCHESTRATION WITH APACHE AIRFLOW/TAG and DAG/dag_and_tags_questions.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DAG and Tags" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,12 +434,12 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Correct Answer</t>
+          <t>Explanation</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Explanation</t>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
@@ -454,15 +454,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Directed Acyclic Graph</t>
+          <t>DAG represents a workflow with directed dependencies and no cycles.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>DAG represents a workflow with directed dependencies and no cycles.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -477,15 +476,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Categorization</t>
+          <t>Tags help organize and filter DAGs in the UI.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tags help organize and filter DAGs in the UI.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -500,15 +498,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>tags</t>
+          <t>The tags parameter accepts a list of strings.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>The tags parameter accepts a list of strings.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -523,15 +520,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Invalid</t>
+          <t>Airflow validates DAGs and cycles make them invalid.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Airflow validates DAGs and cycles make them invalid.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -546,15 +542,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Frequency</t>
+          <t>It defines how often the DAG runs.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>It defines how often the DAG runs.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -569,15 +564,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>No default; must be specified or set to None.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>No default; must be specified or set to None.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -592,15 +586,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>'0 2 * * *'</t>
+          <t>Use cron expression '0 2 * * *'.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Use cron expression '0 2 * * *'.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -615,15 +608,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Backfilling</t>
+          <t>It determines whether to backfill past schedule intervals.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>It determines whether to backfill past schedule intervals.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -638,15 +630,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Skip past runs</t>
+          <t>Only the latest DAG run will be scheduled.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Only the latest DAG run will be scheduled.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -661,15 +652,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Unique identifier</t>
+          <t>Each DAG must have a unique ID.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Each DAG must have a unique ID.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -691,12 +681,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>DAG IDs must be unique across all DAGs.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>DAG IDs must be unique across all DAGs.</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -711,15 +701,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>No limit</t>
+          <t>There is no hard limit on the number of tags.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>There is no hard limit on the number of tags.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -734,15 +723,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Filter bar</t>
+          <t>Tags appear as filter options in the UI.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tags appear as filter options in the UI.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -757,15 +745,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Nested workflow</t>
+          <t>A subDAG is a DAG that runs inside another DAG.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>A subDAG is a DAG that runs inside another DAG.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -780,15 +767,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>No cycles</t>
+          <t>Dependencies must not create circular references.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dependencies must not create circular references.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -803,15 +789,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Shared parameters</t>
+          <t>It provides default parameters for all tasks in the DAG.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>It provides default parameters for all tasks in the DAG.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -826,15 +811,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>start_date</t>
+          <t>The start_date defines when the DAG begins scheduling.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>The start_date defines when the DAG begins scheduling.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -849,15 +833,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Time vs frequency</t>
+          <t>Start date is the start time; schedule_interval is frequency.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Start date is the start time; schedule_interval is frequency.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -879,12 +862,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>DAGs are created in paused state by default.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>DAGs are created in paused state by default.</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -899,15 +882,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>It adds Markdown documentation to the DAG.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>It adds Markdown documentation to the DAG.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
